--- a/output/pdf_financials_xlsx/JVR.P.xlsx
+++ b/output/pdf_financials_xlsx/JVR.P.xlsx
@@ -2563,16 +2563,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.072265</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.072265</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.072265</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.072265</v>
       </c>
     </row>
     <row r="93">
@@ -3796,7 +3796,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -4104,7 +4108,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JVR.P.xlsx
+++ b/output/pdf_financials_xlsx/JVR.P.xlsx
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.08475000000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.352849</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.318547</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.293911</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.236874</v>
       </c>
     </row>
     <row r="35">
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.08475000000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.352849</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.318547</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.293911</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.236874</v>
       </c>
     </row>
     <row r="37">
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.08475000000000001</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.352849</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/JVR.P.xlsx
+++ b/output/pdf_financials_xlsx/JVR.P.xlsx
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.015679</v>
+        <v>0.015984</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.014236</v>
+        <v>0.015462</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.014236</v>
+        <v>0.015462</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.015679</v>
+        <v>0.015984</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.014236</v>
+        <v>0.015462</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.014236</v>
+        <v>0.015462</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -664,13 +664,13 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.015679</v>
+        <v>-0.015984</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.014236</v>
+        <v>-0.015462</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.014236</v>
+        <v>-0.015462</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -5379,7 +5379,11 @@
           <t>General &amp; office expenses 2,100</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -5918,7 +5922,11 @@
           <t>General &amp; office expenses</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
